--- a/data/xlsx/aeosib--electrical-installation-and-maintenance-shipbuilding.xlsx
+++ b/data/xlsx/aeosib--electrical-installation-and-maintenance-shipbuilding.xlsx
@@ -185,9 +185,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -226,6 +223,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -484,89 +484,89 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15.17" customWidth="1" style="15" min="1" max="1"/>
-    <col width="38.4" customWidth="1" style="16" min="2" max="2"/>
+    <col width="38.4" customWidth="1" style="31" min="2" max="2"/>
     <col width="13.72" customWidth="1" style="15" min="3" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="17">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="16">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Course-wise Training Infrastructure and Facilities</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="26.85" customHeight="1" s="17">
-      <c r="A3" s="19" t="inlineStr">
+    <row r="3" ht="26.85" customHeight="1" s="16">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Course Name:</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Electrical Installation and Maintenance (Shipbuilding)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="26.25" customHeight="1" s="17">
-      <c r="A4" s="19" t="inlineStr">
+    <row r="4" ht="26.25" customHeight="1" s="16">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Number of Trainees:</t>
         </is>
       </c>
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="18" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="17">
-      <c r="A6" s="20" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="16">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Course-wise Training Space (Theoretical Classroom, Workshop/ Lab/ Classroom cum Workshop)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="17">
-      <c r="B7" s="19" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="16">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Course Name</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-    </row>
-    <row r="8" ht="51.75" customHeight="1" s="17">
-      <c r="B8" s="19" t="inlineStr">
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+    </row>
+    <row r="8" ht="51.75" customHeight="1" s="16">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Electrical Installation and Maintenance (Shipbuilding)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Classroom – 350 sft (33 sqm)
 Workshop/ lab – 800 sft (75 sq) OR
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="17">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="16">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Major Training Equipment and Training Facilities</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="115.5" customHeight="1" s="17">
-      <c r="A13" s="24" t="inlineStr">
+    <row r="13" ht="115.5" customHeight="1" s="16">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>•The institute shall not use the same facilities for any other projects/organizations offering a similar course.
 •The institute must provide sufficient evidence to prove ownership of the proposed training equipment.
@@ -576,623 +576,671 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="26.25" customHeight="1" s="17">
-      <c r="A15" s="25" t="inlineStr">
+    <row r="15" ht="26.25" customHeight="1" s="16">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>S.N.</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Major Equipment and Training facilities</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>Required facilities</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>Available facilities</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>Weights
 (out of 10)</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>Weighted scores</t>
         </is>
       </c>
-      <c r="G15" s="25" t="inlineStr">
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="13.5" customHeight="1" s="17">
-      <c r="A16" s="26" t="n">
+    <row r="16" ht="13.5" customHeight="1" s="16">
+      <c r="A16" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Wiring Boards/Trainer Board</t>
         </is>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="28" t="n">
+      <c r="D16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="27">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
         <v/>
       </c>
-      <c r="G16" s="28" t="n"/>
-    </row>
-    <row r="17" ht="13.5" customHeight="1" s="17">
-      <c r="A17" s="26" t="n">
+      <c r="G16" s="27" t="n"/>
+    </row>
+    <row r="17" ht="13.5" customHeight="1" s="16">
+      <c r="A17" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Navigation lights</t>
         </is>
       </c>
-      <c r="C17" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" s="28" t="n"/>
-      <c r="E17" s="28" t="n">
+      <c r="C17" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="27">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
         <v/>
       </c>
-      <c r="G17" s="28" t="n"/>
-    </row>
-    <row r="18" ht="13.5" customHeight="1" s="17">
-      <c r="A18" s="26" t="n">
+      <c r="G17" s="27" t="n"/>
+    </row>
+    <row r="18" ht="13.5" customHeight="1" s="16">
+      <c r="A18" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Echo sounder</t>
         </is>
       </c>
-      <c r="C18" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" s="28" t="n"/>
-      <c r="E18" s="28" t="n">
+      <c r="C18" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="27">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
         <v/>
       </c>
-      <c r="G18" s="28" t="n"/>
-    </row>
-    <row r="19" ht="13.5" customHeight="1" s="17">
-      <c r="A19" s="26" t="n">
+      <c r="G18" s="27" t="n"/>
+    </row>
+    <row r="19" ht="13.5" customHeight="1" s="16">
+      <c r="A19" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Magnetic compass</t>
         </is>
       </c>
-      <c r="C19" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" s="28" t="n"/>
-      <c r="E19" s="28" t="n">
+      <c r="C19" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="27">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
         <v/>
       </c>
-      <c r="G19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="13.5" customHeight="1" s="17">
-      <c r="A20" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="G19" s="27" t="n"/>
+    </row>
+    <row r="20" ht="13.5" customHeight="1" s="16">
+      <c r="A20" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>GPS recorder</t>
         </is>
       </c>
-      <c r="C20" s="28" t="n"/>
-      <c r="D20" s="28" t="n"/>
-      <c r="E20" s="28" t="n">
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="27">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
         <v/>
       </c>
-      <c r="G20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="26.85" customHeight="1" s="17">
-      <c r="A21" s="26" t="n">
+      <c r="G20" s="27" t="n"/>
+    </row>
+    <row r="21" ht="26.85" customHeight="1" s="16">
+      <c r="A21" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Main Distribution Board with busbar, CB and other accessories (Training model)</t>
         </is>
       </c>
-      <c r="C21" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" s="28" t="n"/>
-      <c r="E21" s="28" t="n">
+      <c r="C21" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="27">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
         <v/>
       </c>
-      <c r="G21" s="28" t="n"/>
-    </row>
-    <row r="22" ht="26.85" customHeight="1" s="17">
-      <c r="A22" s="26" t="n">
+      <c r="G21" s="27" t="n"/>
+    </row>
+    <row r="22" ht="26.85" customHeight="1" s="16">
+      <c r="A22" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Sub Distribution Board with busbar, CB and other accessories (Training model)</t>
         </is>
       </c>
-      <c r="C22" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" s="28" t="n"/>
-      <c r="E22" s="28" t="n">
+      <c r="C22" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="27">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
         <v/>
       </c>
-      <c r="G22" s="28" t="n"/>
-    </row>
-    <row r="23" ht="13.5" customHeight="1" s="17">
-      <c r="A23" s="26" t="n">
+      <c r="G22" s="27" t="n"/>
+    </row>
+    <row r="23" ht="13.5" customHeight="1" s="16">
+      <c r="A23" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Electric drill machine</t>
         </is>
       </c>
-      <c r="C23" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" s="28" t="n"/>
-      <c r="E23" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" s="28">
+      <c r="C23" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="27">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
         <v/>
       </c>
-      <c r="G23" s="28" t="n"/>
-    </row>
-    <row r="24" ht="13.5" customHeight="1" s="17">
-      <c r="A24" s="26" t="n">
+      <c r="G23" s="27" t="n"/>
+    </row>
+    <row r="24" ht="13.5" customHeight="1" s="16">
+      <c r="A24" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Electric grinding machine</t>
         </is>
       </c>
-      <c r="C24" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="28" t="n"/>
-      <c r="E24" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="28">
+      <c r="C24" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="27">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
         <v/>
       </c>
-      <c r="G24" s="28" t="n"/>
-    </row>
-    <row r="25" ht="13.5" customHeight="1" s="17">
-      <c r="A25" s="26" t="n">
+      <c r="G24" s="27" t="n"/>
+    </row>
+    <row r="25" ht="13.5" customHeight="1" s="16">
+      <c r="A25" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Energy Meter (1 Phase)</t>
         </is>
       </c>
-      <c r="C25" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" s="28" t="n"/>
-      <c r="E25" s="28" t="n">
+      <c r="C25" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="27">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
         <v/>
       </c>
-      <c r="G25" s="28" t="n"/>
-    </row>
-    <row r="26" ht="13.5" customHeight="1" s="17">
-      <c r="A26" s="26" t="n">
+      <c r="G25" s="27" t="n"/>
+    </row>
+    <row r="26" ht="13.5" customHeight="1" s="16">
+      <c r="A26" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Energy Meter (3 Phase)</t>
         </is>
       </c>
-      <c r="C26" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" s="28" t="n"/>
-      <c r="E26" s="28" t="n">
+      <c r="C26" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F26" s="28">
+      <c r="F26" s="27">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
         <v/>
       </c>
-      <c r="G26" s="28" t="n"/>
-    </row>
-    <row r="27" ht="13.5" customHeight="1" s="17">
-      <c r="A27" s="26" t="n">
+      <c r="G26" s="27" t="n"/>
+    </row>
+    <row r="27" ht="13.5" customHeight="1" s="16">
+      <c r="A27" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>Earth tester</t>
         </is>
       </c>
-      <c r="C27" s="28" t="n">
+      <c r="C27" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="28" t="n"/>
-      <c r="E27" s="28" t="n">
+      <c r="D27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="27">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
         <v/>
       </c>
-      <c r="G27" s="28" t="n"/>
-    </row>
-    <row r="28" ht="13.5" customHeight="1" s="17">
-      <c r="A28" s="26" t="n">
+      <c r="G27" s="27" t="n"/>
+    </row>
+    <row r="28" ht="13.5" customHeight="1" s="16">
+      <c r="A28" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Megger</t>
         </is>
       </c>
-      <c r="C28" s="28" t="n">
+      <c r="C28" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="28" t="n"/>
-      <c r="E28" s="28" t="n">
+      <c r="D28" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="27">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
         <v/>
       </c>
-      <c r="G28" s="28" t="n"/>
-    </row>
-    <row r="29" ht="13.5" customHeight="1" s="17">
-      <c r="A29" s="26" t="n">
+      <c r="G28" s="27" t="n"/>
+    </row>
+    <row r="29" ht="13.5" customHeight="1" s="16">
+      <c r="A29" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>Phase sequence meter</t>
         </is>
       </c>
-      <c r="C29" s="28" t="n">
+      <c r="C29" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="28" t="n"/>
-      <c r="E29" s="28" t="n">
+      <c r="D29" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="27">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
         <v/>
       </c>
-      <c r="G29" s="28" t="n"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1" s="17">
-      <c r="A30" s="26" t="n">
+      <c r="G29" s="27" t="n"/>
+    </row>
+    <row r="30" ht="13.5" customHeight="1" s="16">
+      <c r="A30" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Three phase motor (5-10HP)</t>
         </is>
       </c>
-      <c r="C30" s="28" t="n">
+      <c r="C30" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="D30" s="28" t="n"/>
-      <c r="E30" s="28" t="n">
+      <c r="D30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="F30" s="28">
+      <c r="F30" s="27">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
         <v/>
       </c>
-      <c r="G30" s="28" t="n"/>
-    </row>
-    <row r="31" ht="13.5" customHeight="1" s="17">
-      <c r="A31" s="26" t="n">
+      <c r="G30" s="27" t="n"/>
+    </row>
+    <row r="31" ht="13.5" customHeight="1" s="16">
+      <c r="A31" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="B31" s="27" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Single Phase Motor</t>
         </is>
       </c>
-      <c r="C31" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D31" s="28" t="n"/>
-      <c r="E31" s="28" t="n">
+      <c r="C31" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="27">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
         <v/>
       </c>
-      <c r="G31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1" s="17">
-      <c r="A32" s="26" t="n">
+      <c r="G31" s="27" t="n"/>
+    </row>
+    <row r="32" ht="13.5" customHeight="1" s="16">
+      <c r="A32" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="B32" s="27" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>Burnt/Defective motor</t>
         </is>
       </c>
-      <c r="C32" s="28" t="n">
+      <c r="C32" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="28" t="n"/>
-      <c r="E32" s="28" t="n">
+      <c r="D32" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="27">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
         <v/>
       </c>
-      <c r="G32" s="28" t="n"/>
-    </row>
-    <row r="33" ht="13.5" customHeight="1" s="17">
-      <c r="A33" s="26" t="n">
+      <c r="G32" s="27" t="n"/>
+    </row>
+    <row r="33" ht="13.5" customHeight="1" s="16">
+      <c r="A33" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>ATS</t>
         </is>
       </c>
-      <c r="C33" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D33" s="28" t="n"/>
-      <c r="E33" s="28" t="n">
+      <c r="C33" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="27">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
         <v/>
       </c>
-      <c r="G33" s="28" t="n"/>
-    </row>
-    <row r="34" ht="13.5" customHeight="1" s="17">
-      <c r="A34" s="26" t="n">
+      <c r="G33" s="27" t="n"/>
+    </row>
+    <row r="34" ht="13.5" customHeight="1" s="16">
+      <c r="A34" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>DOL Starter</t>
         </is>
       </c>
-      <c r="C34" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D34" s="28" t="n"/>
-      <c r="E34" s="28" t="n">
+      <c r="C34" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="F34" s="28">
+      <c r="F34" s="27">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
         <v/>
       </c>
-      <c r="G34" s="28" t="n"/>
-    </row>
-    <row r="35" ht="26.85" customHeight="1" s="17">
-      <c r="A35" s="26" t="n">
+      <c r="G34" s="27" t="n"/>
+    </row>
+    <row r="35" ht="26.85" customHeight="1" s="16">
+      <c r="A35" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="B35" s="27" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>Star-Delta Starter with controlling arrangement</t>
         </is>
       </c>
-      <c r="C35" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D35" s="28" t="n"/>
-      <c r="E35" s="28" t="n">
+      <c r="C35" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="F35" s="28">
+      <c r="F35" s="27">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
         <v/>
       </c>
-      <c r="G35" s="28" t="n"/>
-    </row>
-    <row r="36" ht="13.5" customHeight="1" s="17">
-      <c r="A36" s="26" t="n">
+      <c r="G35" s="27" t="n"/>
+    </row>
+    <row r="36" ht="13.5" customHeight="1" s="16">
+      <c r="A36" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>Generator (15-25KW)</t>
         </is>
       </c>
-      <c r="C36" s="28" t="n">
+      <c r="C36" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="28" t="n"/>
-      <c r="E36" s="28" t="n">
+      <c r="D36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="F36" s="28">
+      <c r="F36" s="27">
         <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
         <v/>
       </c>
-      <c r="G36" s="28" t="n"/>
-    </row>
-    <row r="37" ht="13.5" customHeight="1" s="17">
-      <c r="A37" s="26" t="n">
+      <c r="G36" s="27" t="n"/>
+    </row>
+    <row r="37" ht="13.5" customHeight="1" s="16">
+      <c r="A37" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="B37" s="27" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Lead Acid Battery (12 V, 100 AH)</t>
         </is>
       </c>
-      <c r="C37" s="28" t="n">
+      <c r="C37" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="28" t="n"/>
-      <c r="E37" s="28" t="n">
+      <c r="D37" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F37" s="28">
+      <c r="F37" s="27">
         <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
         <v/>
       </c>
-      <c r="G37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="26.85" customHeight="1" s="17">
-      <c r="A38" s="26" t="n">
+      <c r="G37" s="27" t="n"/>
+    </row>
+    <row r="38" ht="26.85" customHeight="1" s="16">
+      <c r="A38" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="B38" s="27" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>Forward-Reverse circuit arrangement for motor control</t>
         </is>
       </c>
-      <c r="C38" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="28" t="n">
+      <c r="C38" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F38" s="28">
+      <c r="F38" s="27">
         <f>IFERROR(MIN(C38,D38)*E38/C38,0)</f>
         <v/>
       </c>
-      <c r="G38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="13.5" customHeight="1" s="17">
-      <c r="A39" s="26" t="n">
+      <c r="G38" s="27" t="n"/>
+    </row>
+    <row r="39" ht="13.5" customHeight="1" s="16">
+      <c r="A39" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="B39" s="27" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>Wiring Boards/Trainer Board</t>
         </is>
       </c>
-      <c r="C39" s="28" t="n">
+      <c r="C39" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="D39" s="28" t="n"/>
-      <c r="E39" s="28" t="n">
+      <c r="D39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="F39" s="28">
+      <c r="F39" s="27">
         <f>IFERROR(MIN(C39,D39)*E39/C39,0)</f>
         <v/>
       </c>
-      <c r="G39" s="28" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="17">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="G39" s="27" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="16">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B40" s="22" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="30" t="n"/>
-      <c r="E40" s="29">
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="29" t="n"/>
+      <c r="E40" s="28">
         <f>SUM(E16:E39)</f>
         <v/>
       </c>
-      <c r="F40" s="29">
+      <c r="F40" s="28">
         <f>SUM(F16:F39)</f>
         <v/>
       </c>
-      <c r="G40" s="31" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="17">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="G40" s="30" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="16">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
       </c>
-      <c r="B41" s="22" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="30" t="n"/>
-      <c r="F41" s="29">
+      <c r="B41" s="21" t="n"/>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="29" t="n"/>
+      <c r="F41" s="28">
         <f>F40/E40*100</f>
         <v/>
       </c>
-      <c r="G41" s="31" t="n"/>
-    </row>
-    <row r="42" ht="9.75" customHeight="1" s="17">
+      <c r="G41" s="30" t="n"/>
+    </row>
+    <row r="42" ht="9.75" customHeight="1" s="16">
       <c r="A42" s="15" t="n"/>
     </row>
-    <row r="43" ht="15" customHeight="1" s="17">
-      <c r="A43" s="29" t="inlineStr">
+    <row r="43" ht="15" customHeight="1" s="16">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
       </c>
-      <c r="B43" s="22" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="30" t="n"/>
-      <c r="F43" s="29">
+      <c r="B43" s="21" t="n"/>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="29" t="n"/>
+      <c r="F43" s="28">
         <f>F41*30/100</f>
         <v/>
       </c>
-      <c r="G43" s="29" t="inlineStr">
+      <c r="G43" s="28" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
